--- a/resources/DSA_Cohort3_0_Problem_Links_Complete.xlsx
+++ b/resources/DSA_Cohort3_0_Problem_Links_Complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0933cbe12f1f8942/Desktop/Java DSA/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_5FB5A8CD7175688348676C56415DCE3A8744EE53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{025EE1CF-4877-465F-88B6-CE48EF16F289}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_5FB5A8CD7175688348676C56415DCE3A8744EE53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB076586-405D-4D2C-9418-0CB7E8378F7B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3784,7 +3784,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -3838,8 +3838,11 @@
       <c r="I50" s="10">
         <v>46219</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -3867,8 +3870,11 @@
       <c r="I51" s="10">
         <v>46219</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -3896,8 +3902,11 @@
       <c r="I52" s="10">
         <v>46219</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -3925,8 +3934,11 @@
       <c r="I53" s="10">
         <v>46219</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -3951,8 +3963,14 @@
       <c r="H54" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I54" s="10">
+        <v>46219</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3977,8 +3995,14 @@
       <c r="H55" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I55" s="10">
+        <v>46219</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -4003,8 +4027,14 @@
       <c r="H56" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I56" s="10">
+        <v>46219</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -4030,7 +4060,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -4056,7 +4086,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -4082,7 +4112,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -4108,7 +4138,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -4134,7 +4164,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -4160,7 +4190,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -4186,7 +4216,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>

--- a/resources/DSA_Cohort3_0_Problem_Links_Complete.xlsx
+++ b/resources/DSA_Cohort3_0_Problem_Links_Complete.xlsx
@@ -2229,6 +2229,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
